--- a/VerveStacks_FRA_grids_syn_5/Sets-vervestacks.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9163DF55-2FA2-4664-BA13-5C20A84A1E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFF94CE0-1DDB-4A4D-B08C-976957798FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2147,7 +2147,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57115EC8-FB3D-47E2-BA55-A389FAF56E4A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF98DDBC-593C-4634-94BC-50B1E80FE2EB}">
   <dimension ref="B9:E170"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_syn_5/Sets-vervestacks.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFF94CE0-1DDB-4A4D-B08C-976957798FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8717C511-4A93-4ADE-A934-BCC832459696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2147,7 +2147,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF98DDBC-593C-4634-94BC-50B1E80FE2EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{195E3C7F-B990-42C0-AE70-C0FA01F6CC55}">
   <dimension ref="B9:E170"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_syn_5/Sets-vervestacks.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8717C511-4A93-4ADE-A934-BCC832459696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D514A54-48A2-4D90-94E5-D655C47D3176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2147,7 +2147,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{195E3C7F-B990-42C0-AE70-C0FA01F6CC55}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5934516E-172C-4DA4-A865-B4D6FD730D40}">
   <dimension ref="B9:E170"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_syn_5/Sets-vervestacks.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D514A54-48A2-4D90-94E5-D655C47D3176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{12561AE1-FF0C-456C-A7A9-535D22B96471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2147,7 +2147,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5934516E-172C-4DA4-A865-B4D6FD730D40}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB427607-E9F0-4871-AEF2-D9298C500D37}">
   <dimension ref="B9:E170"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
